--- a/data/trans_camb/IP19C03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 20,93</t>
+          <t>-15,67; 22,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 30,48</t>
+          <t>-8,45; 28,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 39,72</t>
+          <t>3,08; 39,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 21,79</t>
+          <t>-15,54; 21,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 7,78</t>
+          <t>-24,41; 11,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 27,42</t>
+          <t>-10,02; 27,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 16,91</t>
+          <t>-10,92; 16,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 12,85</t>
+          <t>-12,0; 13,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 27,25</t>
+          <t>-0,4; 26,76</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-69,49; 353,54</t>
+          <t>-66,82; 351,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 528,04</t>
+          <t>-41,23; 441,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 619,56</t>
+          <t>3,68; 632,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,59; 177,41</t>
+          <t>-48,64; 187,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,52; 74,04</t>
+          <t>-79,14; 120,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 219,64</t>
+          <t>-32,66; 236,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,72; 132,42</t>
+          <t>-40,08; 138,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,33; 96,93</t>
+          <t>-45,45; 115,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 208,63</t>
+          <t>-3,42; 228,67</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-24,52; -4,08</t>
+          <t>-24,13; -3,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 11,79</t>
+          <t>-12,38; 12,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 19,82</t>
+          <t>-7,9; 22,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 9,54</t>
+          <t>-14,15; 9,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 19,11</t>
+          <t>-6,14; 18,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 14,81</t>
+          <t>-9,19; 17,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,27; -0,27</t>
+          <t>-15,49; 0,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 12,17</t>
+          <t>-5,82; 12,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 13,99</t>
+          <t>-5,25; 13,74</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-86,43; -17,58</t>
+          <t>-87,79; -16,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 76,92</t>
+          <t>-46,84; 89,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 127,94</t>
+          <t>-31,53; 150,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 61,61</t>
+          <t>-53,13; 60,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 114,49</t>
+          <t>-21,89; 122,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 93,28</t>
+          <t>-34,28; 106,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,16; 0,9</t>
+          <t>-61,37; 3,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 71,84</t>
+          <t>-22,45; 73,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,63; 75,07</t>
+          <t>-20,26; 79,77</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-29,85; -0,12</t>
+          <t>-29,85; 0,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-32,45; -2,22</t>
+          <t>-33,47; -3,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-33,17; -4,25</t>
+          <t>-32,67; -2,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 7,56</t>
+          <t>-16,55; 7,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 6,49</t>
+          <t>-18,48; 7,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 13,05</t>
+          <t>-14,6; 12,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 0,77</t>
+          <t>-19,3; -0,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,69; -1,96</t>
+          <t>-21,2; -1,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 1,38</t>
+          <t>-19,1; 1,42</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-86,0; 14,57</t>
+          <t>-87,23; 13,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-92,97; 4,33</t>
+          <t>-93,32; 7,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,78; -10,29</t>
+          <t>-89,42; -8,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-75,94; 92,55</t>
+          <t>-75,8; 109,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,01; 85,08</t>
+          <t>-84,53; 117,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,81; 162,23</t>
+          <t>-67,51; 155,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-73,29; 9,77</t>
+          <t>-72,85; -2,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,98; -8,34</t>
+          <t>-82,43; -6,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,62; 12,72</t>
+          <t>-73,22; 15,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 20,83</t>
+          <t>-8,09; 22,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 13,45</t>
+          <t>-13,99; 12,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 14,51</t>
+          <t>-15,11; 13,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 19,3</t>
+          <t>-7,32; 19,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 10,84</t>
+          <t>-11,75; 11,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 15,63</t>
+          <t>-13,93; 14,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 15,55</t>
+          <t>-2,6; 17,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 7,2</t>
+          <t>-9,3; 8,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 9,62</t>
+          <t>-11,66; 9,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 154,24</t>
+          <t>-29,96; 156,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,06; 95,39</t>
+          <t>-50,83; 92,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,41; 98,35</t>
+          <t>-57,79; 95,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,81; 297,64</t>
+          <t>-41,84; 272,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-64,38; 181,38</t>
+          <t>-61,52; 170,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,16; 195,13</t>
+          <t>-75,66; 189,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 117,37</t>
+          <t>-14,14; 136,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 57,42</t>
+          <t>-42,8; 65,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 81,27</t>
+          <t>-56,19; 72,25</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 10,84</t>
+          <t>-22,0; 11,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 34,93</t>
+          <t>-13,12; 32,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 12,16</t>
+          <t>-19,21; 11,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 3,52</t>
+          <t>-31,83; 1,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 25,62</t>
+          <t>-20,64; 24,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 5,59</t>
+          <t>-26,61; 6,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 1,95</t>
+          <t>-21,67; 1,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 20,59</t>
+          <t>-10,47; 19,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 4,16</t>
+          <t>-17,95; 4,7</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-81,05; 159,66</t>
+          <t>-81,04; 137,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-51,91; 330,71</t>
+          <t>-53,97; 331,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-69,85; 150,42</t>
+          <t>-66,71; 129,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-91,51; 100,87</t>
+          <t>-93,8; 49,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,96; 269,58</t>
+          <t>-68,77; 219,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-83,55; 66,41</t>
+          <t>-80,37; 82,95</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-78,88; 17,94</t>
+          <t>-79,76; 14,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 150,07</t>
+          <t>-42,53; 148,21</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-65,79; 33,85</t>
+          <t>-63,89; 42,65</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 11,93</t>
+          <t>-22,65; 11,91</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-32,46; -3,23</t>
+          <t>-32,49; -3,96</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-30,2; 3,62</t>
+          <t>-26,44; 2,38</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 15,59</t>
+          <t>-10,84; 16,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 9,75</t>
+          <t>-13,94; 8,89</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 16,91</t>
+          <t>-10,48; 16,21</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 10,57</t>
+          <t>-11,2; 9,34</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -0,25</t>
+          <t>-18,47; 0,31</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 6,21</t>
+          <t>-16,23; 5,34</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-73,11; 106,1</t>
+          <t>-68,24; 118,64</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-94,4; 0,2</t>
+          <t>-95,17; -6,52</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-88,02; 62,54</t>
+          <t>-86,6; 31,23</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-72,75; 344,35</t>
+          <t>-67,41; 344,68</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-82,72; 255,59</t>
+          <t>-80,45; 204,21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-70,1; 470,11</t>
+          <t>-76,03; 329,01</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-50,37; 105,03</t>
+          <t>-51,2; 92,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-82,99; 6,87</t>
+          <t>-81,82; 8,58</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-69,37; 61,44</t>
+          <t>-70,03; 50,32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 14,39</t>
+          <t>-6,87; 13,99</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-18,27; -1,16</t>
+          <t>-17,54; -0,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 13,27</t>
+          <t>-6,27; 13,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 10,83</t>
+          <t>-8,92; 11,17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 8,83</t>
+          <t>-10,74; 9,56</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 14,67</t>
+          <t>-4,54; 15,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 9,72</t>
+          <t>-4,52; 10,06</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 1,39</t>
+          <t>-11,5; 1,6</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 12,6</t>
+          <t>-1,82; 12,34</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 155,37</t>
+          <t>-36,06; 159,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-90,52; -0,5</t>
+          <t>-90,85; 11,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 147,55</t>
+          <t>-34,12; 154,12</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-48,35; 121,64</t>
+          <t>-44,7; 140,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 90,42</t>
+          <t>-60,93; 114,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,57; 157,14</t>
+          <t>-26,2; 168,38</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 88,63</t>
+          <t>-26,74; 98,91</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-67,03; 14,2</t>
+          <t>-66,8; 16,29</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 116,87</t>
+          <t>-11,18; 120,0</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,78; 23,63</t>
+          <t>0,95; 23,77</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 12,21</t>
+          <t>-9,16; 12,03</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-27,55; -9,37</t>
+          <t>-27,12; -9,66</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,53; 24,49</t>
+          <t>2,13; 25,73</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 17,89</t>
+          <t>-2,81; 18,65</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-21,29; -5,59</t>
+          <t>-21,93; -5,85</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,25; 20,11</t>
+          <t>4,7; 21,39</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 12,4</t>
+          <t>-3,53; 12,31</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-23,09; -10,28</t>
+          <t>-21,59; -9,91</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2,61; 123,1</t>
+          <t>2,2; 124,53</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 63,76</t>
+          <t>-29,75; 62,76</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-89,29; -45,0</t>
+          <t>-88,72; -43,49</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10,11; 168,93</t>
+          <t>8,28; 183,37</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 127,96</t>
+          <t>-12,49; 132,78</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-87,77; -32,05</t>
+          <t>-87,09; -34,97</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,64; 111,97</t>
+          <t>19,14; 119,76</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 68,07</t>
+          <t>-13,76; 63,86</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-84,77; -52,95</t>
+          <t>-84,07; -53,53</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 5,29</t>
+          <t>-5,18; 4,42</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 1,02</t>
+          <t>-8,46; 0,81</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 1,33</t>
+          <t>-7,82; 1,89</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 6,51</t>
+          <t>-2,76; 6,56</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,66</t>
+          <t>-4,12; 5,02</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 3,86</t>
+          <t>-5,36; 3,73</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 4,12</t>
+          <t>-2,45; 4,37</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 1,81</t>
+          <t>-4,86; 2,08</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,9</t>
+          <t>-5,62; 1,28</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 29,39</t>
+          <t>-22,41; 23,74</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 6,31</t>
+          <t>-36,81; 3,98</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-33,46; 6,82</t>
+          <t>-34,09; 10,73</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 43,07</t>
+          <t>-14,58; 42,17</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 29,7</t>
+          <t>-21,09; 32,55</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 25,27</t>
+          <t>-27,76; 24,09</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 24,06</t>
+          <t>-12,37; 25,28</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 10,4</t>
+          <t>-23,22; 12,21</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 5,49</t>
+          <t>-27,12; 7,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 22,41</t>
+          <t>-16,46; 22,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 28,63</t>
+          <t>-7,89; 31,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 39,61</t>
+          <t>1,51; 37,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 21,17</t>
+          <t>-14,81; 22,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,41; 11,28</t>
+          <t>-27,01; 7,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 27,64</t>
+          <t>-11,07; 28,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 16,27</t>
+          <t>-8,89; 16,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 13,59</t>
+          <t>-11,54; 14,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 26,76</t>
+          <t>0,09; 27,96</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,82; 351,7</t>
+          <t>-73,51; 452,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-41,23; 441,6</t>
+          <t>-38,62; 444,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 632,31</t>
+          <t>-1,31; 621,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 187,92</t>
+          <t>-49,09; 172,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,14; 120,37</t>
+          <t>-79,95; 81,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 236,21</t>
+          <t>-37,31; 234,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,08; 138,37</t>
+          <t>-36,13; 135,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,45; 115,27</t>
+          <t>-44,69; 129,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 228,67</t>
+          <t>1,17; 244,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-24,13; -3,15</t>
+          <t>-25,31; -4,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 12,48</t>
+          <t>-13,92; 11,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 22,38</t>
+          <t>-7,67; 20,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 9,6</t>
+          <t>-15,63; 8,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 18,88</t>
+          <t>-7,38; 18,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 17,59</t>
+          <t>-11,07; 16,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 0,54</t>
+          <t>-16,35; -0,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 12,08</t>
+          <t>-5,42; 11,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 13,74</t>
+          <t>-5,52; 13,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-87,79; -16,07</t>
+          <t>-87,5; -17,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,84; 89,09</t>
+          <t>-49,62; 67,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,53; 150,83</t>
+          <t>-27,1; 136,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,13; 60,18</t>
+          <t>-56,28; 51,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 122,6</t>
+          <t>-27,29; 115,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,28; 106,33</t>
+          <t>-43,08; 96,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 3,26</t>
+          <t>-62,78; -0,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 73,32</t>
+          <t>-22,11; 65,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 79,77</t>
+          <t>-22,65; 73,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 0,83</t>
+          <t>-31,04; -1,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-33,47; -3,38</t>
+          <t>-34,3; -3,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-32,67; -2,81</t>
+          <t>-32,57; -3,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 7,79</t>
+          <t>-16,46; 7,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 7,72</t>
+          <t>-20,22; 6,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 12,67</t>
+          <t>-13,81; 13,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,3; -0,73</t>
+          <t>-20,82; -0,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,2; -1,91</t>
+          <t>-22,26; -3,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 1,42</t>
+          <t>-19,63; 1,59</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-87,23; 13,89</t>
+          <t>-88,05; 8,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-93,32; 7,58</t>
+          <t>-100,0; -3,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,42; -8,64</t>
+          <t>-89,24; -7,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-75,8; 109,96</t>
+          <t>-75,38; 94,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-84,53; 117,11</t>
+          <t>-87,03; 117,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,51; 155,62</t>
+          <t>-63,65; 157,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-72,85; -2,42</t>
+          <t>-76,68; -3,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,43; -6,08</t>
+          <t>-85,27; -9,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,22; 15,26</t>
+          <t>-74,03; 14,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 22,03</t>
+          <t>-8,98; 21,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 12,89</t>
+          <t>-14,4; 12,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 13,89</t>
+          <t>-15,67; 14,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 19,41</t>
+          <t>-7,06; 18,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 11,26</t>
+          <t>-12,45; 10,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 14,38</t>
+          <t>-13,8; 16,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 17,04</t>
+          <t>-3,7; 16,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 8,32</t>
+          <t>-10,87; 7,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 9,21</t>
+          <t>-10,89; 9,13</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,96; 156,72</t>
+          <t>-32,52; 144,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,83; 92,79</t>
+          <t>-52,95; 93,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,79; 95,82</t>
+          <t>-59,01; 99,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,84; 272,26</t>
+          <t>-40,77; 256,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,52; 170,91</t>
+          <t>-61,0; 182,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,66; 189,25</t>
+          <t>-70,81; 219,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 136,06</t>
+          <t>-17,13; 127,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,8; 65,83</t>
+          <t>-48,35; 58,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-56,19; 72,25</t>
+          <t>-51,47; 74,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 11,44</t>
+          <t>-21,31; 10,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 32,92</t>
+          <t>-10,69; 35,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 11,33</t>
+          <t>-17,67; 14,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-31,83; 1,1</t>
+          <t>-33,32; -0,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 24,68</t>
+          <t>-21,13; 23,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 6,27</t>
+          <t>-27,73; 5,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 1,24</t>
+          <t>-21,1; 1,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 19,86</t>
+          <t>-9,45; 21,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 4,7</t>
+          <t>-18,95; 4,57</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-81,04; 137,56</t>
+          <t>-80,93; 119,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,97; 331,84</t>
+          <t>-47,31; 353,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-66,71; 129,49</t>
+          <t>-64,03; 178,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-93,8; 49,52</t>
+          <t>-100,0; 51,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-68,77; 219,27</t>
+          <t>-72,27; 216,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-80,37; 82,95</t>
+          <t>-83,07; 66,71</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-79,76; 14,31</t>
+          <t>-80,24; 19,61</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,53; 148,21</t>
+          <t>-37,69; 169,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-63,89; 42,65</t>
+          <t>-67,34; 42,35</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 11,91</t>
+          <t>-23,09; 12,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-32,49; -3,96</t>
+          <t>-32,37; -3,78</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 2,38</t>
+          <t>-31,96; 2,34</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 16,03</t>
+          <t>-11,34; 15,21</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 8,89</t>
+          <t>-14,38; 10,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 16,21</t>
+          <t>-12,0; 16,71</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 9,34</t>
+          <t>-11,38; 9,75</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 0,31</t>
+          <t>-18,96; -0,39</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 5,34</t>
+          <t>-15,02; 6,75</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-68,24; 118,64</t>
+          <t>-69,78; 114,76</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-95,17; -6,52</t>
+          <t>-95,2; -7,4</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-86,6; 31,23</t>
+          <t>-86,99; 47,19</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-67,41; 344,68</t>
+          <t>-74,84; 306,86</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-80,45; 204,21</t>
+          <t>-81,8; 246,26</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-76,03; 329,01</t>
+          <t>-75,91; 371,84</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 92,39</t>
+          <t>-52,91; 99,3</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-81,82; 8,58</t>
+          <t>-81,85; 3,36</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-70,03; 50,32</t>
+          <t>-68,09; 78,81</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 13,99</t>
+          <t>-6,53; 14,05</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-17,54; -0,92</t>
+          <t>-17,46; -1,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 13,89</t>
+          <t>-6,27; 15,09</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 11,17</t>
+          <t>-8,12; 11,83</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 9,56</t>
+          <t>-10,81; 9,99</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 15,2</t>
+          <t>-4,46; 15,91</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 10,06</t>
+          <t>-5,38; 9,97</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 1,6</t>
+          <t>-11,92; 1,57</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 12,34</t>
+          <t>-2,22; 12,06</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-36,06; 159,8</t>
+          <t>-38,03; 161,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-90,85; 11,99</t>
+          <t>-89,99; -1,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-34,12; 154,12</t>
+          <t>-34,22; 170,91</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-44,7; 140,14</t>
+          <t>-44,97; 135,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 114,37</t>
+          <t>-58,9; 113,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,2; 168,38</t>
+          <t>-23,78; 183,47</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 98,91</t>
+          <t>-31,99; 90,36</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-66,8; 16,29</t>
+          <t>-67,23; 18,29</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 120,0</t>
+          <t>-11,9; 118,49</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,95; 23,77</t>
+          <t>1,57; 24,26</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 12,03</t>
+          <t>-8,83; 11,86</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-27,12; -9,66</t>
+          <t>-27,01; -9,74</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,13; 25,73</t>
+          <t>1,05; 24,78</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 18,65</t>
+          <t>-3,76; 18,33</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-21,93; -5,85</t>
+          <t>-21,8; -5,11</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,7; 21,39</t>
+          <t>4,84; 20,95</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 12,31</t>
+          <t>-3,76; 12,0</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-21,59; -9,91</t>
+          <t>-21,96; -10,05</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2,2; 124,53</t>
+          <t>4,33; 131,71</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,75; 62,76</t>
+          <t>-30,36; 60,93</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-88,72; -43,49</t>
+          <t>-89,26; -48,82</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8,28; 183,37</t>
+          <t>5,13; 182,06</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 132,78</t>
+          <t>-15,94; 135,12</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-87,09; -34,97</t>
+          <t>-85,12; -26,75</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,14; 119,76</t>
+          <t>17,62; 110,92</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 63,86</t>
+          <t>-14,55; 63,36</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-84,07; -53,53</t>
+          <t>-83,68; -53,78</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 4,42</t>
+          <t>-5,39; 4,39</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 0,81</t>
+          <t>-8,42; 0,92</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 1,89</t>
+          <t>-8,06; 1,81</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 6,56</t>
+          <t>-2,7; 7,02</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 5,02</t>
+          <t>-3,96; 5,37</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,73</t>
+          <t>-6,16; 3,24</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 4,37</t>
+          <t>-2,59; 3,94</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 2,08</t>
+          <t>-4,9; 1,66</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,28</t>
+          <t>-5,36; 1,14</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 23,74</t>
+          <t>-23,18; 23,69</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 3,98</t>
+          <t>-36,93; 4,65</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-34,09; 10,73</t>
+          <t>-35,53; 9,96</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 42,17</t>
+          <t>-13,5; 46,38</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 32,55</t>
+          <t>-19,48; 35,17</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 24,09</t>
+          <t>-30,57; 21,27</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 25,28</t>
+          <t>-12,0; 22,23</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 12,21</t>
+          <t>-23,47; 9,37</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 7,02</t>
+          <t>-25,74; 6,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-8,46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,43</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>12,27</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20,92</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-8,46</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,72</t>
+          <t>24,48</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,07</t>
+          <t>14,55</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 22,81</t>
+          <t>-16,31; 21,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 31,27</t>
+          <t>-27,81; 7,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 37,76</t>
+          <t>-13,21; 24,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 22,54</t>
+          <t>-15,65; 20,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 7,9</t>
+          <t>-8,01; 30,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 28,07</t>
+          <t>3,04; 41,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 16,58</t>
+          <t>-9,05; 16,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 14,55</t>
+          <t>-11,75; 12,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 27,96</t>
+          <t>1,15; 27,62</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-37,2%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>23,61%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>80,45%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>137,22%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,05%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-37,2%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>160,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-73,51; 452,29</t>
+          <t>-51,59; 177,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,62; 444,25</t>
+          <t>-83,52; 74,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 621,4</t>
+          <t>-44,6; 188,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 172,28</t>
+          <t>-69,49; 353,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,95; 81,71</t>
+          <t>-34,53; 528,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 234,89</t>
+          <t>2,61; 650,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 135,5</t>
+          <t>-37,72; 132,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 129,1</t>
+          <t>-45,33; 96,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 244,12</t>
+          <t>-0,51; 202,5</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,48</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,66</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-13,65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,59</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,48</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>2,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -4,44</t>
+          <t>-13,34; 9,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 11,25</t>
+          <t>-6,25; 19,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 20,24</t>
+          <t>-10,38; 15,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 8,04</t>
+          <t>-24,52; -4,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 18,77</t>
+          <t>-13,36; 11,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 16,06</t>
+          <t>-11,37; 13,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,35; -0,67</t>
+          <t>-16,27; -0,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 11,76</t>
+          <t>-5,71; 12,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 13,66</t>
+          <t>-6,68; 11,68</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-15,08%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29,46%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-62,95%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-2,7%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24,64%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-15,08%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29,46%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-87,5; -17,53</t>
+          <t>-50,82; 61,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 67,8</t>
+          <t>-22,16; 114,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,1; 136,59</t>
+          <t>-38,69; 100,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,28; 51,71</t>
+          <t>-86,43; -17,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 115,76</t>
+          <t>-50,43; 76,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,08; 96,41</t>
+          <t>-39,84; 85,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,78; -0,03</t>
+          <t>-62,16; 0,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 65,4</t>
+          <t>-22,06; 71,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 73,93</t>
+          <t>-27,26; 65,59</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6,53</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,57</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-15,31</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-18,32</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-17,19</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,2</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-6,53</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>-16,55</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-8,81</t>
+          <t>-8,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-31,04; -1,77</t>
+          <t>-17,59; 7,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-34,3; -3,55</t>
+          <t>-18,81; 6,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-32,57; -3,69</t>
+          <t>-14,5; 12,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 7,73</t>
+          <t>-29,85; -0,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 6,58</t>
+          <t>-32,45; -2,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 13,32</t>
+          <t>-32,98; -3,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,82; -0,93</t>
+          <t>-19,13; 0,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,26; -3,34</t>
+          <t>-21,69; -1,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 1,59</t>
+          <t>-18,3; 1,42</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-26,51%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-41,24%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-9,91%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-59,28%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-70,93%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-66,55%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-26,51%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-41,24%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-7,95%</t>
+          <t>-64,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-42,45%</t>
+          <t>-42,6%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-88,05; 8,29</t>
+          <t>-75,94; 92,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -3,36</t>
+          <t>-86,01; 85,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,24; -7,54</t>
+          <t>-68,95; 153,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-75,38; 94,44</t>
+          <t>-86,0; 14,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,03; 117,39</t>
+          <t>-92,97; 4,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,65; 157,62</t>
+          <t>-88,88; -2,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,68; -3,53</t>
+          <t>-73,29; 9,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,27; -9,8</t>
+          <t>-83,98; -8,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-74,03; 14,67</t>
+          <t>-70,6; 13,24</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,73</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6,49</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,83</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,95</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,54</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-2,27</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-1,0</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 21,62</t>
+          <t>-7,09; 19,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 12,05</t>
+          <t>-12,67; 10,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 14,53</t>
+          <t>-12,01; 16,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 18,91</t>
+          <t>-8,77; 20,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 10,79</t>
+          <t>-13,57; 13,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 16,08</t>
+          <t>-15,94; 13,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 16,74</t>
+          <t>-4,56; 15,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 7,67</t>
+          <t>-9,69; 7,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 9,13</t>
+          <t>-10,34; 10,12</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>41,47%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-4,12%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>30,48%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-3,92%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-9,16%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-4,12%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-10,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-8,22%</t>
+          <t>-5,78%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 144,41</t>
+          <t>-38,81; 297,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-52,95; 93,67</t>
+          <t>-64,38; 181,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,01; 99,09</t>
+          <t>-65,94; 212,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,77; 256,28</t>
+          <t>-30,91; 154,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,0; 182,06</t>
+          <t>-50,06; 95,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,81; 219,09</t>
+          <t>-60,76; 95,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 127,39</t>
+          <t>-21,16; 117,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,35; 58,33</t>
+          <t>-45,78; 57,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,47; 74,67</t>
+          <t>-52,4; 83,57</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-14,21</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,98</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-10,07</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-4,91</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>9,72</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,78</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-14,21</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-10,24</t>
+          <t>-1,68</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,28</t>
+          <t>-6,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 10,88</t>
+          <t>-30,57; 3,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 35,77</t>
+          <t>-19,22; 25,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 14,46</t>
+          <t>-28,18; 5,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-33,32; -0,01</t>
+          <t>-21,39; 10,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 23,28</t>
+          <t>-11,06; 34,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 5,3</t>
+          <t>-19,52; 12,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 1,95</t>
+          <t>-21,66; 1,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 21,21</t>
+          <t>-10,73; 20,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 4,57</t>
+          <t>-18,31; 4,6</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-65,04%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-46,08%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-26,65%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>52,76%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-9,68%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-65,04%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-46,88%</t>
+          <t>-9,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-31,36%</t>
+          <t>-30,15%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-80,93; 119,05</t>
+          <t>-91,51; 100,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,31; 353,86</t>
+          <t>-66,96; 269,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-64,03; 178,04</t>
+          <t>-83,31; 65,41</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 51,09</t>
+          <t>-81,05; 159,66</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-72,27; 216,46</t>
+          <t>-51,91; 330,71</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-83,07; 66,71</t>
+          <t>-68,94; 149,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-80,24; 19,61</t>
+          <t>-78,88; 17,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 169,68</t>
+          <t>-43,22; 150,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-67,34; 42,35</t>
+          <t>-65,19; 38,27</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>2,36</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-1,61</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1,53</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-4,36</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-17,02</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-11,75</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>-11,41</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-4,59</t>
+          <t>-4,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 12,01</t>
+          <t>-10,99; 15,59</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-32,37; -3,78</t>
+          <t>-14,31; 9,75</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 2,34</t>
+          <t>-10,98; 16,15</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 15,21</t>
+          <t>-23,43; 11,93</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 10,72</t>
+          <t>-32,46; -3,23</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 16,71</t>
+          <t>-29,79; 4,2</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 9,75</t>
+          <t>-11,26; 10,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-18,96; -0,39</t>
+          <t>-19,48; -0,25</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 6,75</t>
+          <t>-15,68; 6,05</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>21,52%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-14,72%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>13,94%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-19,57%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-76,43%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-52,75%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>21,52%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-14,72%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>-51,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-28,13%</t>
+          <t>-28,68%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-69,78; 114,76</t>
+          <t>-72,75; 344,35</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-95,2; -7,4</t>
+          <t>-82,72; 255,59</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-86,99; 47,19</t>
+          <t>-70,11; 460,16</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-74,84; 306,86</t>
+          <t>-73,11; 106,1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-81,8; 246,26</t>
+          <t>-94,4; 0,2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-75,91; 371,84</t>
+          <t>-87,63; 64,42</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-52,91; 99,3</t>
+          <t>-50,37; 105,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-81,85; 3,36</t>
+          <t>-82,99; 6,87</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 78,81</t>
+          <t>-69,55; 59,46</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,66</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,12</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5,98</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>3,16</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-8,72</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>4,61</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,12</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>5,83</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 14,05</t>
+          <t>-8,6; 10,83</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-17,46; -1,44</t>
+          <t>-11,19; 8,83</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 15,09</t>
+          <t>-5,84; 14,98</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 11,83</t>
+          <t>-8,1; 14,39</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 9,99</t>
+          <t>-18,27; -1,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 15,91</t>
+          <t>-6,04; 15,01</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 9,97</t>
+          <t>-4,49; 9,72</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 1,57</t>
+          <t>-11,22; 1,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 12,06</t>
+          <t>-1,44; 13,13</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>11,84%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-8,02%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>42,71%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>22,68%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-62,59%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-8,02%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>41,72%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-38,03; 161,7</t>
+          <t>-48,35; 121,64</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-89,99; -1,99</t>
+          <t>-63,75; 90,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 170,91</t>
+          <t>-30,72; 159,16</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 135,65</t>
+          <t>-44,96; 155,37</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-58,9; 113,75</t>
+          <t>-90,52; -0,5</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 183,47</t>
+          <t>-32,18; 161,05</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-31,99; 90,36</t>
+          <t>-26,59; 88,63</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-67,23; 18,29</t>
+          <t>-67,03; 14,2</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 118,49</t>
+          <t>-9,47; 121,13</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>13,52</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>7,61</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-13,98</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>12,18</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1,41</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-18,44</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>13,52</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>7,61</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-13,45</t>
+          <t>-18,93</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-16,07</t>
+          <t>-16,58</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,57; 24,26</t>
+          <t>2,53; 24,49</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 11,86</t>
+          <t>-2,75; 17,89</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-27,01; -9,74</t>
+          <t>-21,87; -6,29</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,05; 24,78</t>
+          <t>0,78; 23,63</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 18,33</t>
+          <t>-10,39; 12,21</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-21,8; -5,11</t>
+          <t>-28,05; -10,11</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,84; 20,95</t>
+          <t>4,25; 20,11</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 12,0</t>
+          <t>-3,65; 12,4</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-21,96; -10,05</t>
+          <t>-23,46; -11,12</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>69,62%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>39,19%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-71,99%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>49,37%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-74,73%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>69,62%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>39,19%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-69,22%</t>
+          <t>-76,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-72,51%</t>
+          <t>-74,82%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>4,33; 131,71</t>
+          <t>10,11; 168,93</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 60,93</t>
+          <t>-10,8; 127,96</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-89,26; -48,82</t>
+          <t>-89,54; -37,27</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5,13; 182,06</t>
+          <t>2,61; 123,1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 135,12</t>
+          <t>-35,05; 63,76</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-85,12; -26,75</t>
+          <t>-90,56; -47,57</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,62; 110,92</t>
+          <t>16,64; 111,97</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 63,36</t>
+          <t>-14,33; 68,07</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-83,68; -53,78</t>
+          <t>-86,35; -57,16</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-1,74</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-3,75</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-3,15</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-3,76</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-2,77</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 4,39</t>
+          <t>-3,23; 6,51</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 0,92</t>
+          <t>-3,74; 4,66</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 1,81</t>
+          <t>-6,02; 3,32</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 7,02</t>
+          <t>-5,0; 5,29</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 5,37</t>
+          <t>-8,38; 1,02</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 3,24</t>
+          <t>-8,51; 0,66</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 3,94</t>
+          <t>-2,32; 4,12</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 1,66</t>
+          <t>-4,76; 1,81</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 1,14</t>
+          <t>-6,04; 0,48</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-9,93%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-0,47%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-18,06%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-15,17%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-7,31%</t>
+          <t>-18,11%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-11,83%</t>
+          <t>-14,49%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 23,69</t>
+          <t>-16,11; 43,07</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 4,65</t>
+          <t>-18,81; 29,7</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 9,96</t>
+          <t>-30,54; 22,43</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 46,38</t>
+          <t>-22,88; 29,39</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 35,17</t>
+          <t>-35,96; 6,31</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 21,27</t>
+          <t>-36,3; 3,55</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 22,23</t>
+          <t>-11,1; 24,06</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 9,37</t>
+          <t>-22,96; 10,4</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 6,74</t>
+          <t>-29,06; 3,04</t>
         </is>
       </c>
     </row>
